--- a/docs/resource-template.xlsx
+++ b/docs/resource-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\workA\codework\yuban\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C83F7A-0CC6-4D48-8CE9-81086BAA004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801330D9-40C9-4C4A-B5CB-0FE37D5EDE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>資源名稱</t>
   </si>
@@ -61,129 +61,29 @@
     <t>注意事項</t>
   </si>
   <si>
-    <t>台北市政府提供的兒童與家庭資源入口頁</t>
-  </si>
-  <si>
-    <t>連結入口</t>
-  </si>
-  <si>
-    <t>政府</t>
-  </si>
-  <si>
-    <t>台北市政府</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>全齡</t>
-  </si>
-  <si>
-    <t>生活照護</t>
-  </si>
-  <si>
-    <t>政府資源, 入口頁</t>
-  </si>
-  <si>
-    <t>人工核實</t>
-  </si>
-  <si>
-    <t>政府機構發布，內容可作為入口參考</t>
-  </si>
-  <si>
-    <t>請以官方資訊為主，必要時再確認最新內容</t>
-  </si>
-  <si>
-    <t>新生兒睡眠基礎指南</t>
-  </si>
-  <si>
-    <t>介紹新生兒睡眠節律與安全睡眠做法</t>
-  </si>
-  <si>
-    <t>文章</t>
-  </si>
-  <si>
-    <t>個人創作者</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>0–1歲</t>
-  </si>
-  <si>
-    <t>睡眠</t>
-  </si>
-  <si>
-    <t>AI 整理・待人工核實</t>
-  </si>
-  <si>
-    <t>內容需再確認來源可信度</t>
-  </si>
-  <si>
-    <t>請以實際原始來源為準</t>
-  </si>
-  <si>
-    <t>https://welfare.gov.taipei/Kids/Home/Index</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>台北市育兒網</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>親子天下</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>親子社群平台</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>連結入口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育教養解決方案</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育教養</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.parenting.com.tw/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>華文圈影響力最大的教育教養品牌</t>
-  </si>
-  <si>
-    <t>https://hao-mong.tw/sleep-of-newborn-and-infant/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Blog</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>新生兒, 睡眠</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>年齡群組</t>
+  </si>
+  <si>
+    <t>地區</t>
+  </si>
+  <si>
+    <t>資源類型</t>
+  </si>
+  <si>
+    <t>使用對象</t>
+  </si>
+  <si>
+    <t>來源地區</t>
+  </si>
+  <si>
+    <t>語言</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,21 +105,6 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF393939"/>
-      <name val="Noto Sans TC"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -238,19 +123,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,25 +431,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="39.59765625" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="22.5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="21.296875" customWidth="1"/>
-    <col min="10" max="10" width="19.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="29.5" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="4" customWidth="1"/>
+    <col min="16" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -608,131 +492,27 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{8BEE9A56-245D-44E6-A7C8-17B256CFF128}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{E75A4B57-D8C9-4436-956F-C290FE0B8250}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{3FEB25B0-740A-4DAF-8C07-51F3E836F318}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>